--- a/10.Модули и библиотеки/student_works/report.xlsx
+++ b/10.Модули и библиотеки/student_works/report.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Статистика по годам" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Статистика по городам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +46,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,229 +427,234 @@
   </sheetPr>
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Средняя зарплата</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Количество вакансий</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>38595</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>45020</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>38639</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2" t="n">
         <v>44574</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>275</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>51269</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>383</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="2" t="n">
         <v>49240</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>414</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
         <v>48842</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>603</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="2" t="n">
         <v>49654</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>671</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="2" t="n">
         <v>50633</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>698</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="2" t="n">
         <v>55200</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>729</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="2" t="n">
         <v>61733</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>842</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="2" t="n">
         <v>57249</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>1309</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="2" t="n">
         <v>67999</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>1185</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="2" t="n">
         <v>75369</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>1003</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="2" t="n">
         <v>81305</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>602</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="2" t="n">
         <v>93485</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>197</v>
       </c>
     </row>
@@ -656,223 +671,217 @@
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Город</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Уровень зарплат</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Город</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Доля вакансий, %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>78400</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>32.09</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Санкт-Петербург</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>65503</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Санкт-Петербург</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>11.77</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Екатеринбург</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>63641</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Новосибирск</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>2.64</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Новосибирск</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2" t="n">
         <v>57484</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Томск</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>57364</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>2.55</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="2" t="n">
         <v>53700</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Ростов-на-Дону</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>2.21</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Пермь</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
         <v>53163</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Екатеринбург</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Самара</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="2" t="n">
         <v>51304</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Краснодар</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>1.98</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Нижний Новгород</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="2" t="n">
         <v>49290</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Самара</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>1.49</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Казань</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="2" t="n">
         <v>49067</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Воронеж</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Пермь</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>1.34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>